--- a/2026/O HIGGINS 1157/Mayo/Mayo ohiggins.xlsx
+++ b/2026/O HIGGINS 1157/Mayo/Mayo ohiggins.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\O HIGGINS 1157\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\O HIGGINS 1157\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54385EE8-C872-4E30-8D4D-1E8E122ADBD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABA1A4DA-6A04-40DA-BBA6-779655AB9A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -22,16 +22,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$124</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="219">
   <si>
     <t>TOTAL</t>
   </si>
@@ -208,9 +203,6 @@
     <t>NOMBRE:</t>
   </si>
   <si>
-    <t>Ferraro jose</t>
-  </si>
-  <si>
     <t>QUEJA VIA:</t>
   </si>
   <si>
@@ -223,58 +215,10 @@
     <t>MOTIVO DE LA QUEJA:</t>
   </si>
   <si>
-    <t>El 10 C habia abonado en el mes 4 $132.420,71 , le quedaban $3677 pesos a favor y la pusimos impaga - Debe abonar $130.084,71</t>
-  </si>
-  <si>
-    <t>El 10A deposito $220.300 el 08/05</t>
-  </si>
-  <si>
-    <t>10A</t>
-  </si>
-  <si>
-    <t>Cristina_Kruk@hotmail.com</t>
-  </si>
-  <si>
-    <t>Cristina</t>
-  </si>
-  <si>
-    <t>Deposito 15/05 $147.000</t>
-  </si>
-  <si>
-    <t>8C creo</t>
-  </si>
-  <si>
-    <t>Angelica</t>
-  </si>
-  <si>
-    <t>Deposito $160.000 el 19/05 (creo)</t>
-  </si>
-  <si>
-    <t>6F</t>
-  </si>
-  <si>
-    <t>Gustavo Peker</t>
-  </si>
-  <si>
-    <t>9B</t>
-  </si>
-  <si>
     <t>VTO 18/06</t>
   </si>
   <si>
     <t>PERÍODO: MAYO</t>
-  </si>
-  <si>
-    <t>11C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremy </t>
-  </si>
-  <si>
-    <t>El 11C mando un mail explicando su situacion y sus pagos - desde jeremynaguel@gmail.com - Revisar</t>
-  </si>
-  <si>
-    <t>Abono $180.866,63 el 27/04 y no lo pusimos pago. CHEQUEAR - Tranfririo el 28/05 $182.697,63</t>
   </si>
   <si>
     <t>CUIT DEL EDIFICIO: 33-71743270-9</t>
@@ -739,6 +683,18 @@
   </si>
   <si>
     <t>ARCA P. De pago:</t>
+  </si>
+  <si>
+    <t>2A , COCHERA 7 Y COCHERA 18</t>
+  </si>
+  <si>
+    <t>Estudio M&amp;M</t>
+  </si>
+  <si>
+    <t>2A , COCHERA 7 Y COCHERA 18 TRANSFIRIO $449.413 EL DIA 04/06</t>
+  </si>
+  <si>
+    <t>Myryam Martinez Del Valle</t>
   </si>
 </sst>
 </file>
@@ -755,7 +711,7 @@
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -911,16 +867,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="18">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -995,30 +943,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74FA84"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1522,12 +1446,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="260">
+  <cellXfs count="236">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1747,36 +1670,11 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="7" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1791,15 +1689,13 @@
     <xf numFmtId="167" fontId="18" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="18" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1817,7 +1713,7 @@
     <xf numFmtId="8" fontId="11" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1830,14 +1726,10 @@
     <xf numFmtId="44" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="1" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1845,6 +1737,12 @@
     <xf numFmtId="44" fontId="1" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1890,114 +1788,111 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2017,8 +1912,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
+  <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -2100,9 +1994,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2140,9 +2034,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2175,26 +2069,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2227,26 +2104,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2421,31 +2281,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
   <dimension ref="A1:M125"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.7109375" customWidth="1"/>
+    <col min="10" max="10" width="22.6640625" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
-      <c r="B1" s="203" t="s">
-        <v>82</v>
-      </c>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="204"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" s="180" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="E1" s="181"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="10" t="s">
         <v>46</v>
@@ -2454,16 +2314,16 @@
       <c r="D2" s="4"/>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:5" ht="56.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="56.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
-      <c r="B3" s="207" t="s">
-        <v>166</v>
-      </c>
-      <c r="C3" s="207"/>
-      <c r="D3" s="207"/>
-      <c r="E3" s="208"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="184" t="s">
+        <v>149</v>
+      </c>
+      <c r="C3" s="184"/>
+      <c r="D3" s="184"/>
+      <c r="E3" s="185"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
@@ -2474,12 +2334,12 @@
       <c r="D4" s="8"/>
       <c r="E4" s="9"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="4" t="s">
@@ -2487,7 +2347,7 @@
       </c>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="84" t="s">
         <v>38</v>
       </c>
@@ -2498,57 +2358,57 @@
       </c>
       <c r="E6" s="9"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="209" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" s="209"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="209"/>
-      <c r="C9" s="209"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="209"/>
-      <c r="C10" s="209"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="210" t="s">
-        <v>167</v>
-      </c>
-      <c r="B13" s="210"/>
-      <c r="C13" s="210"/>
-      <c r="D13" s="210"/>
-      <c r="E13" s="210"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="210"/>
-      <c r="B14" s="210"/>
-      <c r="C14" s="210"/>
-      <c r="D14" s="210"/>
-      <c r="E14" s="210"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="210"/>
-      <c r="B15" s="210"/>
-      <c r="C15" s="210"/>
-      <c r="D15" s="210"/>
-      <c r="E15" s="210"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="210"/>
-      <c r="B16" s="210"/>
-      <c r="C16" s="210"/>
-      <c r="D16" s="210"/>
-      <c r="E16" s="210"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="186" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="186"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="186"/>
+      <c r="C9" s="186"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="186"/>
+      <c r="C10" s="186"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="187" t="s">
+        <v>150</v>
+      </c>
+      <c r="B13" s="187"/>
+      <c r="C13" s="187"/>
+      <c r="D13" s="187"/>
+      <c r="E13" s="187"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="187"/>
+      <c r="B14" s="187"/>
+      <c r="C14" s="187"/>
+      <c r="D14" s="187"/>
+      <c r="E14" s="187"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="187"/>
+      <c r="B15" s="187"/>
+      <c r="C15" s="187"/>
+      <c r="D15" s="187"/>
+      <c r="E15" s="187"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="187"/>
+      <c r="B16" s="187"/>
+      <c r="C16" s="187"/>
+      <c r="D16" s="187"/>
+      <c r="E16" s="187"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
         <v>7</v>
       </c>
@@ -2557,52 +2417,52 @@
       <c r="D20" s="15"/>
       <c r="E20" s="16"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
       <c r="D21" s="103"/>
       <c r="E21" s="121"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="205" t="s">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="182" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="206"/>
+      <c r="B22" s="183"/>
       <c r="C22" s="20"/>
-      <c r="D22" s="188">
+      <c r="D22" s="163">
         <v>1199023.2</v>
       </c>
       <c r="E22" s="122"/>
       <c r="H22" s="21"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="205" t="s">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="182" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="206"/>
+      <c r="B23" s="183"/>
       <c r="C23" s="20"/>
-      <c r="D23" s="188">
+      <c r="D23" s="163">
         <v>-260787.54</v>
       </c>
       <c r="E23" s="22"/>
       <c r="H23" s="21"/>
     </row>
-    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="205" t="s">
+    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="182" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="206"/>
+      <c r="B24" s="183"/>
       <c r="C24" s="20"/>
-      <c r="D24" s="189">
+      <c r="D24" s="164">
         <v>0.34</v>
       </c>
       <c r="E24" s="22"/>
       <c r="H24" s="21"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="23" t="s">
         <v>8</v>
       </c>
@@ -2614,7 +2474,7 @@
         <v>938235.99999999988</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="23" t="s">
         <v>53</v>
       </c>
@@ -2623,28 +2483,28 @@
       <c r="D26" s="24"/>
       <c r="E26" s="124"/>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="20"/>
       <c r="B27" s="20"/>
       <c r="C27" s="20"/>
       <c r="D27" s="36"/>
       <c r="E27" s="136"/>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="20"/>
       <c r="B28" s="20"/>
       <c r="C28" s="20"/>
       <c r="D28" s="36"/>
       <c r="E28" s="136"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="20"/>
       <c r="B29" s="20"/>
       <c r="C29" s="20"/>
       <c r="D29" s="36"/>
       <c r="E29" s="136"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="23" t="s">
         <v>8</v>
       </c>
@@ -2656,7 +2516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="17" t="s">
         <v>39</v>
       </c>
@@ -2665,9 +2525,9 @@
       <c r="D31" s="24"/>
       <c r="E31" s="124"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="B32" s="85"/>
       <c r="C32" s="85"/>
@@ -2675,27 +2535,27 @@
         <v>641302.6</v>
       </c>
       <c r="E32" s="125" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="G32" s="67"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="B33" s="182" t="s">
-        <v>188</v>
+        <v>170</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>171</v>
       </c>
       <c r="C33" s="85"/>
       <c r="D33" s="36">
         <v>182823.01</v>
       </c>
       <c r="E33" s="125" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="G33" s="67"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="20" t="s">
         <v>41</v>
       </c>
@@ -2705,11 +2565,11 @@
         <v>58593.37</v>
       </c>
       <c r="E34" s="125" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G34" s="67"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="20" t="s">
         <v>43</v>
       </c>
@@ -2724,7 +2584,7 @@
       </c>
       <c r="G35" s="51"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="20" t="s">
         <v>42</v>
       </c>
@@ -2738,7 +2598,7 @@
         <v>Debito 12/05</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="23" t="s">
         <v>40</v>
       </c>
@@ -2750,7 +2610,7 @@
         <v>992022.5</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="17" t="s">
         <v>9</v>
       </c>
@@ -2759,26 +2619,26 @@
       <c r="D38" s="25"/>
       <c r="E38" s="126"/>
     </row>
-    <row r="39" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="211" t="s">
-        <v>89</v>
-      </c>
-      <c r="B39" s="212"/>
+    <row r="39" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="188" t="s">
+        <v>72</v>
+      </c>
+      <c r="B39" s="189"/>
       <c r="C39" s="28"/>
-      <c r="D39" s="187">
+      <c r="D39" s="162">
         <v>205033.71</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="211" t="s">
-        <v>90</v>
-      </c>
-      <c r="B40" s="212"/>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="188" t="s">
+        <v>73</v>
+      </c>
+      <c r="B40" s="189"/>
       <c r="C40" s="28"/>
-      <c r="D40" s="187">
+      <c r="D40" s="162">
         <v>1282.32</v>
       </c>
       <c r="E40" s="22" t="str">
@@ -2786,13 +2646,13 @@
         <v>Debito Autom.</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="211" t="s">
-        <v>91</v>
-      </c>
-      <c r="B41" s="212"/>
+    <row r="41" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="188" t="s">
+        <v>74</v>
+      </c>
+      <c r="B41" s="189"/>
       <c r="C41" s="28"/>
-      <c r="D41" s="187">
+      <c r="D41" s="162">
         <v>12020</v>
       </c>
       <c r="E41" s="22" t="str">
@@ -2800,7 +2660,7 @@
         <v>Debito Autom.</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="23" t="s">
         <v>10</v>
       </c>
@@ -2812,7 +2672,7 @@
         <v>218336.03</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="17" t="s">
         <v>11</v>
       </c>
@@ -2821,57 +2681,57 @@
       <c r="D43" s="30"/>
       <c r="E43" s="127"/>
     </row>
-    <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="31" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="B44" s="31"/>
       <c r="C44" s="31"/>
-      <c r="D44" s="186">
+      <c r="D44" s="161">
         <v>997677.51</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="31" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="B45" s="32"/>
       <c r="C45" s="31"/>
-      <c r="D45" s="186">
+      <c r="D45" s="161">
         <v>6087.49</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="211" t="s">
-        <v>88</v>
-      </c>
-      <c r="B46" s="212"/>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="188" t="s">
+        <v>71</v>
+      </c>
+      <c r="B46" s="189"/>
       <c r="C46" s="31"/>
-      <c r="D46" s="186">
+      <c r="D46" s="161">
         <v>570397.97</v>
       </c>
       <c r="E46" s="104" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="33" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="B47" s="27"/>
       <c r="C47" s="31"/>
-      <c r="D47" s="186">
+      <c r="D47" s="161">
         <v>0</v>
       </c>
       <c r="E47" s="22"/>
     </row>
-    <row r="48" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="23" t="s">
         <v>12</v>
       </c>
@@ -2883,180 +2743,180 @@
         <v>1574162.97</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="17" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B49" s="23"/>
       <c r="C49" s="23"/>
       <c r="D49" s="24"/>
       <c r="E49" s="129"/>
     </row>
-    <row r="50" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="205" t="s">
-        <v>181</v>
-      </c>
-      <c r="B50" s="206"/>
+    <row r="50" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="182" t="s">
+        <v>164</v>
+      </c>
+      <c r="B50" s="183"/>
       <c r="C50" s="31"/>
-      <c r="D50" s="186">
+      <c r="D50" s="161">
         <v>250600</v>
       </c>
       <c r="E50" s="35" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="205" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="182" t="s">
+        <v>158</v>
+      </c>
+      <c r="B51" s="183"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="161">
+        <v>367392.3</v>
+      </c>
+      <c r="E51" s="35" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="182" t="s">
+        <v>173</v>
+      </c>
+      <c r="B52" s="183"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="161">
+        <v>2130000</v>
+      </c>
+      <c r="E52" s="35" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="158" t="s">
         <v>175</v>
-      </c>
-      <c r="B51" s="206"/>
-      <c r="C51" s="31"/>
-      <c r="D51" s="186">
-        <v>367392.3</v>
-      </c>
-      <c r="E51" s="35" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="205" t="s">
-        <v>190</v>
-      </c>
-      <c r="B52" s="206"/>
-      <c r="C52" s="31"/>
-      <c r="D52" s="186">
-        <v>2130000</v>
-      </c>
-      <c r="E52" s="35" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="181" t="s">
-        <v>192</v>
       </c>
       <c r="B53" s="19"/>
       <c r="C53" s="20"/>
-      <c r="D53" s="186">
+      <c r="D53" s="161">
         <v>73000</v>
       </c>
       <c r="E53" s="35" t="s">
+        <v>159</v>
+      </c>
+      <c r="F53" s="51"/>
+    </row>
+    <row r="54" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="87" t="s">
+        <v>177</v>
+      </c>
+      <c r="B54" s="19"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="161">
+        <v>840000</v>
+      </c>
+      <c r="E54" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="F54" s="51"/>
+    </row>
+    <row r="55" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="190" t="s">
+        <v>161</v>
+      </c>
+      <c r="B55" s="191"/>
+      <c r="C55" s="20"/>
+      <c r="D55" s="161">
+        <v>4400</v>
+      </c>
+      <c r="E55" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="F55" s="51"/>
+    </row>
+    <row r="56" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="87" t="s">
         <v>176</v>
       </c>
-      <c r="F53" s="51"/>
-    </row>
-    <row r="54" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="87" t="s">
-        <v>194</v>
-      </c>
-      <c r="B54" s="169"/>
-      <c r="C54" s="20"/>
-      <c r="D54" s="186">
-        <v>840000</v>
-      </c>
-      <c r="E54" s="35" t="s">
-        <v>195</v>
-      </c>
-      <c r="F54" s="51"/>
-    </row>
-    <row r="55" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="213" t="s">
-        <v>178</v>
-      </c>
-      <c r="B55" s="214"/>
-      <c r="C55" s="20"/>
-      <c r="D55" s="186">
-        <v>4400</v>
-      </c>
-      <c r="E55" s="35" t="s">
-        <v>177</v>
-      </c>
-      <c r="F55" s="51"/>
-    </row>
-    <row r="56" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="87" t="s">
-        <v>193</v>
-      </c>
-      <c r="B56" s="169"/>
+      <c r="B56" s="19"/>
       <c r="C56" s="20"/>
-      <c r="D56" s="186">
+      <c r="D56" s="161">
         <v>60500</v>
       </c>
       <c r="E56" s="35" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="87" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="B57" s="19"/>
       <c r="C57" s="20"/>
-      <c r="D57" s="186">
+      <c r="D57" s="161">
         <v>28000</v>
       </c>
       <c r="E57" s="135" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="F57" s="51"/>
     </row>
-    <row r="58" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="87" t="s">
-        <v>196</v>
-      </c>
-      <c r="B58" s="169"/>
+        <v>179</v>
+      </c>
+      <c r="B58" s="19"/>
       <c r="C58" s="20"/>
-      <c r="D58" s="186">
+      <c r="D58" s="161">
         <v>10400</v>
       </c>
       <c r="E58" s="135" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="F58" s="51"/>
     </row>
-    <row r="59" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="205" t="s">
-        <v>198</v>
-      </c>
-      <c r="B59" s="206"/>
+    <row r="59" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="182" t="s">
+        <v>181</v>
+      </c>
+      <c r="B59" s="183"/>
       <c r="C59" s="20"/>
-      <c r="D59" s="186">
+      <c r="D59" s="161">
         <v>50000</v>
       </c>
       <c r="E59" s="135" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="F59" s="51"/>
     </row>
-    <row r="60" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="205" t="s">
-        <v>180</v>
-      </c>
-      <c r="B60" s="206"/>
+    <row r="60" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="182" t="s">
+        <v>163</v>
+      </c>
+      <c r="B60" s="183"/>
       <c r="C60" s="20"/>
-      <c r="D60" s="186">
+      <c r="D60" s="161">
         <v>127000</v>
       </c>
       <c r="E60" s="135" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="F60" s="51"/>
     </row>
-    <row r="61" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="205" t="s">
-        <v>182</v>
-      </c>
-      <c r="B61" s="206"/>
+    <row r="61" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="182" t="s">
+        <v>165</v>
+      </c>
+      <c r="B61" s="183"/>
       <c r="C61" s="20"/>
-      <c r="D61" s="186">
+      <c r="D61" s="161">
         <v>7200</v>
       </c>
       <c r="E61" s="135" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="F61" s="51"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="23" t="s">
         <v>0</v>
       </c>
@@ -3068,7 +2928,7 @@
         <v>3948492.3</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="17" t="s">
         <v>13</v>
       </c>
@@ -3077,55 +2937,55 @@
       <c r="D63" s="18"/>
       <c r="E63" s="121"/>
     </row>
-    <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="205" t="s">
-        <v>199</v>
-      </c>
-      <c r="B64" s="206"/>
+    <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="182" t="s">
+        <v>182</v>
+      </c>
+      <c r="B64" s="183"/>
       <c r="C64" s="20"/>
-      <c r="D64" s="190">
+      <c r="D64" s="165">
         <v>0</v>
       </c>
       <c r="E64" s="122"/>
     </row>
-    <row r="65" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="205" t="s">
-        <v>184</v>
-      </c>
-      <c r="B65" s="206"/>
+    <row r="65" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="182" t="s">
+        <v>167</v>
+      </c>
+      <c r="B65" s="183"/>
       <c r="C65" s="20"/>
-      <c r="D65" s="185">
+      <c r="D65" s="160">
         <v>230000</v>
       </c>
       <c r="E65" s="122" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="205" t="s">
-        <v>185</v>
-      </c>
-      <c r="B66" s="206"/>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="182" t="s">
+        <v>168</v>
+      </c>
+      <c r="B66" s="183"/>
       <c r="C66" s="20"/>
-      <c r="D66" s="185">
+      <c r="D66" s="160">
         <v>460000</v>
       </c>
       <c r="E66" s="122" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="87" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="B67" s="19"/>
       <c r="C67" s="20"/>
-      <c r="D67" s="185">
+      <c r="D67" s="160">
         <v>0</v>
       </c>
       <c r="E67" s="122"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="23" t="s">
         <v>8</v>
       </c>
@@ -3137,7 +2997,7 @@
         <v>690000</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="17" t="s">
         <v>14</v>
       </c>
@@ -3146,9 +3006,9 @@
       <c r="D69" s="39"/>
       <c r="E69" s="42"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="31" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="B70" s="86"/>
       <c r="C70" s="86"/>
@@ -3157,9 +3017,9 @@
       </c>
       <c r="E70" s="130"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="31" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="B71" s="86"/>
       <c r="C71" s="86"/>
@@ -3169,7 +3029,7 @@
       </c>
       <c r="E71" s="130"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="40" t="s">
         <v>8</v>
       </c>
@@ -3181,14 +3041,14 @@
         <v>224963.89</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="31"/>
       <c r="B73" s="31"/>
       <c r="C73" s="31"/>
       <c r="D73" s="43"/>
       <c r="E73" s="44"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="45" t="s">
         <v>15</v>
       </c>
@@ -3197,13 +3057,13 @@
       <c r="D74" s="46"/>
       <c r="E74" s="47"/>
     </row>
-    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="48"/>
       <c r="D75" s="49"/>
       <c r="E75" s="50"/>
       <c r="F75" s="51"/>
     </row>
-    <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="52" t="s">
         <v>16</v>
       </c>
@@ -3217,16 +3077,16 @@
       <c r="F76" s="57"/>
       <c r="G76" s="51"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D77" s="49"/>
       <c r="E77" s="49"/>
     </row>
-    <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D78" s="49"/>
       <c r="E78" s="49"/>
       <c r="H78" s="58"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="12" t="s">
         <v>17</v>
       </c>
@@ -3235,25 +3095,25 @@
       <c r="D79" s="59"/>
       <c r="E79" s="60"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="216"/>
-      <c r="B80" s="217"/>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" s="193"/>
+      <c r="B80" s="194"/>
       <c r="C80" s="31"/>
-      <c r="D80" s="167"/>
-      <c r="E80" s="168"/>
-    </row>
-    <row r="81" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D80" s="145"/>
+      <c r="E80" s="146"/>
+    </row>
+    <row r="81" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D81" s="43"/>
       <c r="E81" s="43"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="26"/>
       <c r="B82" s="62"/>
       <c r="C82" s="31"/>
       <c r="D82" s="36"/>
       <c r="E82" s="61"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="63" t="s">
         <v>45</v>
       </c>
@@ -3265,11 +3125,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D84" s="49"/>
       <c r="E84" s="49"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="45" t="s">
         <v>18</v>
       </c>
@@ -3280,11 +3140,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D86" s="49"/>
       <c r="E86" s="49"/>
     </row>
-    <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="52" t="s">
         <v>19</v>
       </c>
@@ -3296,11 +3156,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D88" s="49"/>
       <c r="E88" s="49"/>
     </row>
-    <row r="89" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="65" t="s">
         <v>20</v>
       </c>
@@ -3311,7 +3171,7 @@
       <c r="D89" s="49"/>
       <c r="E89" s="49"/>
     </row>
-    <row r="90" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="65" t="s">
         <v>21</v>
       </c>
@@ -3322,7 +3182,7 @@
       <c r="D90" s="49"/>
       <c r="E90" s="49"/>
     </row>
-    <row r="91" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="65" t="s">
         <v>22</v>
       </c>
@@ -3333,7 +3193,7 @@
       <c r="D91" s="49"/>
       <c r="E91" s="49"/>
     </row>
-    <row r="92" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="65" t="s">
         <v>23</v>
       </c>
@@ -3344,17 +3204,17 @@
       <c r="D92" s="49"/>
       <c r="E92" s="49"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D93" s="49"/>
       <c r="E93" s="49"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D94" s="49"/>
       <c r="E94" s="49"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="137" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="B95" s="70">
         <v>0</v>
@@ -3362,9 +3222,9 @@
       <c r="D95" s="49"/>
       <c r="E95" s="49"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="28" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="B96" s="71">
         <v>2000000</v>
@@ -3372,15 +3232,15 @@
       <c r="D96" s="49"/>
       <c r="E96" s="49"/>
     </row>
-    <row r="97" spans="1:5" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="28"/>
       <c r="B97" s="120"/>
       <c r="D97" s="49"/>
       <c r="E97" s="49"/>
     </row>
-    <row r="98" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="73" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="B98" s="74">
         <v>2026301.37</v>
@@ -3388,21 +3248,21 @@
       <c r="D98" s="49"/>
       <c r="E98" s="49"/>
     </row>
-    <row r="99" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="191"/>
-      <c r="B99" s="192"/>
+    <row r="99" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="166"/>
+      <c r="B99" s="167"/>
       <c r="D99" s="49"/>
       <c r="E99" s="49"/>
     </row>
-    <row r="100" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="191"/>
-      <c r="B100" s="192"/>
+    <row r="100" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="166"/>
+      <c r="B100" s="167"/>
       <c r="D100" s="49"/>
       <c r="E100" s="49"/>
     </row>
-    <row r="101" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="137" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="B101" s="70">
         <v>231400</v>
@@ -3410,9 +3270,9 @@
       <c r="D101" s="49"/>
       <c r="E101" s="49"/>
     </row>
-    <row r="102" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="28" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="B102" s="71">
         <v>0</v>
@@ -3420,17 +3280,17 @@
       <c r="D102" s="49"/>
       <c r="E102" s="49"/>
     </row>
-    <row r="103" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="28" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="B103" s="120"/>
       <c r="D103" s="49"/>
       <c r="E103" s="49"/>
     </row>
-    <row r="104" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="73" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="B104" s="74">
         <f>SUM(B101:B103)</f>
@@ -3439,15 +3299,15 @@
       <c r="D104" s="49"/>
       <c r="E104" s="49"/>
     </row>
-    <row r="105" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="191"/>
-      <c r="B105" s="192"/>
+    <row r="105" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="166"/>
+      <c r="B105" s="167"/>
       <c r="D105" s="49"/>
       <c r="E105" s="49"/>
     </row>
-    <row r="106" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="137" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="B106" s="70">
         <v>64328</v>
@@ -3455,9 +3315,9 @@
       <c r="D106" s="49"/>
       <c r="E106" s="49"/>
     </row>
-    <row r="107" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="28" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="B107" s="71">
         <v>0</v>
@@ -3465,17 +3325,17 @@
       <c r="D107" s="49"/>
       <c r="E107" s="49"/>
     </row>
-    <row r="108" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="28" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="B108" s="120"/>
       <c r="D108" s="49"/>
       <c r="E108" s="49"/>
     </row>
-    <row r="109" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="73" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="B109" s="74">
         <f>SUM(B106:B108)</f>
@@ -3484,16 +3344,16 @@
       <c r="D109" s="49"/>
       <c r="E109" s="49"/>
     </row>
-    <row r="110" spans="1:5" s="69" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" s="69" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A110"/>
       <c r="B110" s="67"/>
       <c r="C110" s="68"/>
       <c r="D110" s="132"/>
       <c r="E110" s="132"/>
     </row>
-    <row r="111" spans="1:5" s="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" s="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="137" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="B111" s="70">
         <v>4238170</v>
@@ -3502,18 +3362,18 @@
       <c r="D111" s="133"/>
       <c r="E111" s="133"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="B112" s="195">
+      <c r="B112" s="170">
         <f>-B90-B91</f>
         <v>-8586213.6899999995</v>
       </c>
       <c r="D112" s="49"/>
       <c r="E112" s="49"/>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="28" t="s">
         <v>24</v>
       </c>
@@ -3525,7 +3385,7 @@
       <c r="E113" s="49"/>
       <c r="F113" s="67"/>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="28" t="s">
         <v>2</v>
       </c>
@@ -3537,25 +3397,25 @@
       <c r="E114" s="49"/>
       <c r="F114" s="67"/>
     </row>
-    <row r="115" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A115" s="28" t="s">
-        <v>222</v>
-      </c>
-      <c r="B115" s="194">
+        <v>205</v>
+      </c>
+      <c r="B115" s="169">
         <v>1576753.42</v>
       </c>
       <c r="D115" s="49"/>
       <c r="E115" s="49"/>
       <c r="F115" s="67"/>
     </row>
-    <row r="116" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="28"/>
       <c r="B116" s="120"/>
-      <c r="D116" s="193"/>
+      <c r="D116" s="168"/>
       <c r="E116" s="49"/>
       <c r="F116" s="67"/>
     </row>
-    <row r="117" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="73" t="s">
         <v>48</v>
       </c>
@@ -3567,33 +3427,33 @@
       <c r="E117" s="51"/>
       <c r="F117" s="51"/>
     </row>
-    <row r="118" spans="1:13" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="119" spans="1:13" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="196" t="s">
-        <v>223</v>
-      </c>
-      <c r="B119" s="197">
+    <row r="118" spans="1:13" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="119" spans="1:13" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A119" s="171" t="s">
+        <v>206</v>
+      </c>
+      <c r="B119" s="172">
         <f>B117+B104</f>
         <v>4217943.7300000004</v>
       </c>
       <c r="E119" s="51"/>
     </row>
-    <row r="120" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="215" t="s">
+    <row r="120" spans="1:13" ht="21.9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A121" s="192" t="s">
         <v>25</v>
       </c>
-      <c r="B121" s="215"/>
-      <c r="C121" s="215"/>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A122" s="215"/>
-      <c r="B122" s="215"/>
-      <c r="C122" s="215"/>
-    </row>
-    <row r="123" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B121" s="192"/>
+      <c r="C121" s="192"/>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A122" s="192"/>
+      <c r="B122" s="192"/>
+      <c r="C122" s="192"/>
+    </row>
+    <row r="123" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="75" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="B123" s="101">
         <v>156782</v>
@@ -3601,7 +3461,7 @@
       <c r="C123" s="76"/>
       <c r="D123" s="57"/>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" s="77" t="s">
         <v>0</v>
       </c>
@@ -3611,7 +3471,7 @@
       </c>
       <c r="C124" s="79"/>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M125" s="80"/>
     </row>
   </sheetData>
@@ -3649,135 +3509,135 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533DB7A7-09F4-49CF-B824-70F15C1FF525}">
   <dimension ref="A1:R69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="3" width="25.5703125" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="3" width="25.5546875" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
-    <col min="11" max="13" width="14.42578125" customWidth="1"/>
-    <col min="14" max="14" width="12.28515625" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" customWidth="1"/>
-    <col min="17" max="17" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" customWidth="1"/>
+    <col min="10" max="10" width="12.44140625" customWidth="1"/>
+    <col min="11" max="13" width="14.44140625" customWidth="1"/>
+    <col min="14" max="14" width="12.33203125" customWidth="1"/>
+    <col min="15" max="15" width="14.6640625" customWidth="1"/>
+    <col min="16" max="16" width="14.33203125" customWidth="1"/>
+    <col min="17" max="17" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="19" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="88"/>
-      <c r="B1" s="176"/>
+      <c r="B1" s="153"/>
       <c r="C1" s="89"/>
       <c r="D1" s="89"/>
-      <c r="E1" s="199"/>
-      <c r="F1" s="199"/>
-      <c r="G1" s="199"/>
-      <c r="H1" s="199"/>
-      <c r="I1" s="199"/>
-      <c r="J1" s="222" t="str">
+      <c r="E1" s="153"/>
+      <c r="F1" s="153"/>
+      <c r="G1" s="153"/>
+      <c r="H1" s="153"/>
+      <c r="I1" s="153"/>
+      <c r="J1" s="195" t="str">
         <f>RESUMEN!B3</f>
         <v xml:space="preserve">Banco: Santander N.º de cuenta: 039-021152/7
 CBU: 0720039720000002115272
 Alias: EDIFICIO.AIRE.FRESCO
 </v>
       </c>
-      <c r="K1" s="222"/>
-      <c r="L1" s="222"/>
-      <c r="M1" s="222"/>
-      <c r="N1" s="222"/>
-      <c r="O1" s="222"/>
-      <c r="P1" s="223"/>
-    </row>
-    <row r="2" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
+      <c r="P1" s="196"/>
+    </row>
+    <row r="2" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B2" s="177"/>
-      <c r="C2" s="201">
+        <v>208</v>
+      </c>
+      <c r="B2" s="154"/>
+      <c r="C2" s="174">
         <f>R3</f>
         <v>6319499.4800000004</v>
       </c>
       <c r="D2" s="90"/>
       <c r="E2" s="90"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="251"/>
+      <c r="F2" s="205"/>
+      <c r="G2" s="205"/>
       <c r="H2" s="90"/>
       <c r="I2" s="90"/>
-      <c r="J2" s="224"/>
-      <c r="K2" s="224"/>
-      <c r="L2" s="224"/>
-      <c r="M2" s="224"/>
-      <c r="N2" s="224"/>
-      <c r="O2" s="224"/>
-      <c r="P2" s="225"/>
+      <c r="J2" s="197"/>
+      <c r="K2" s="197"/>
+      <c r="L2" s="197"/>
+      <c r="M2" s="197"/>
+      <c r="N2" s="197"/>
+      <c r="O2" s="197"/>
+      <c r="P2" s="198"/>
       <c r="Q2" s="81"/>
       <c r="R2">
         <v>7500000</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="177"/>
-      <c r="C3" s="201">
+      <c r="B3" s="154"/>
+      <c r="C3" s="174">
         <v>0</v>
       </c>
       <c r="D3" s="90"/>
       <c r="E3" s="90"/>
-      <c r="F3" s="184"/>
-      <c r="G3" s="184"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="159"/>
       <c r="H3" s="90"/>
       <c r="I3" s="90"/>
-      <c r="J3" s="224"/>
-      <c r="K3" s="224"/>
-      <c r="L3" s="224"/>
-      <c r="M3" s="224"/>
-      <c r="N3" s="224"/>
-      <c r="O3" s="224"/>
-      <c r="P3" s="225"/>
+      <c r="J3" s="197"/>
+      <c r="K3" s="197"/>
+      <c r="L3" s="197"/>
+      <c r="M3" s="197"/>
+      <c r="N3" s="197"/>
+      <c r="O3" s="197"/>
+      <c r="P3" s="198"/>
       <c r="Q3" s="81"/>
       <c r="R3" s="51">
         <f>R2-C5-C4</f>
         <v>6319499.4800000004</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B4" s="177"/>
-      <c r="C4" s="201">
+        <v>214</v>
+      </c>
+      <c r="B4" s="154"/>
+      <c r="C4" s="174">
         <v>182823.01</v>
       </c>
       <c r="D4" s="90"/>
       <c r="E4" s="90"/>
-      <c r="F4" s="198"/>
-      <c r="G4" s="198"/>
+      <c r="F4" s="159"/>
+      <c r="G4" s="159"/>
       <c r="H4" s="90"/>
       <c r="I4" s="90"/>
-      <c r="J4" s="224"/>
-      <c r="K4" s="224"/>
-      <c r="L4" s="224"/>
-      <c r="M4" s="224"/>
-      <c r="N4" s="224"/>
-      <c r="O4" s="224"/>
-      <c r="P4" s="225"/>
+      <c r="J4" s="197"/>
+      <c r="K4" s="197"/>
+      <c r="L4" s="197"/>
+      <c r="M4" s="197"/>
+      <c r="N4" s="197"/>
+      <c r="O4" s="197"/>
+      <c r="P4" s="198"/>
       <c r="Q4" s="81"/>
       <c r="R4" s="51"/>
     </row>
-    <row r="5" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="200" t="s">
-        <v>226</v>
-      </c>
-      <c r="B5" s="178"/>
-      <c r="C5" s="202">
+    <row r="5" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="173" t="s">
+        <v>209</v>
+      </c>
+      <c r="B5" s="155"/>
+      <c r="C5" s="175">
         <v>997677.51</v>
       </c>
       <c r="D5" s="91"/>
@@ -3786,211 +3646,211 @@
       <c r="G5" s="92"/>
       <c r="H5" s="91"/>
       <c r="I5" s="91"/>
-      <c r="J5" s="226"/>
-      <c r="K5" s="226"/>
-      <c r="L5" s="226"/>
-      <c r="M5" s="226"/>
-      <c r="N5" s="226"/>
-      <c r="O5" s="226"/>
-      <c r="P5" s="227"/>
+      <c r="J5" s="199"/>
+      <c r="K5" s="199"/>
+      <c r="L5" s="199"/>
+      <c r="M5" s="199"/>
+      <c r="N5" s="199"/>
+      <c r="O5" s="199"/>
+      <c r="P5" s="200"/>
       <c r="Q5" s="81"/>
     </row>
-    <row r="6" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="231" t="s">
-        <v>228</v>
-      </c>
-      <c r="B6" s="232"/>
-      <c r="C6" s="233"/>
-      <c r="D6" s="233"/>
-      <c r="E6" s="233"/>
-      <c r="F6" s="233"/>
-      <c r="G6" s="233"/>
-      <c r="H6" s="233"/>
-      <c r="I6" s="233"/>
-      <c r="J6" s="233"/>
-      <c r="K6" s="233"/>
-      <c r="L6" s="233"/>
-      <c r="M6" s="233"/>
-      <c r="N6" s="233"/>
-      <c r="O6" s="233"/>
-      <c r="P6" s="234"/>
+    <row r="6" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="207" t="s">
+        <v>211</v>
+      </c>
+      <c r="B6" s="208"/>
+      <c r="C6" s="209"/>
+      <c r="D6" s="209"/>
+      <c r="E6" s="209"/>
+      <c r="F6" s="209"/>
+      <c r="G6" s="209"/>
+      <c r="H6" s="209"/>
+      <c r="I6" s="209"/>
+      <c r="J6" s="209"/>
+      <c r="K6" s="209"/>
+      <c r="L6" s="209"/>
+      <c r="M6" s="209"/>
+      <c r="N6" s="209"/>
+      <c r="O6" s="209"/>
+      <c r="P6" s="210"/>
       <c r="Q6" s="81"/>
     </row>
-    <row r="7" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="235"/>
-      <c r="B7" s="236"/>
-      <c r="C7" s="237"/>
-      <c r="D7" s="237"/>
-      <c r="E7" s="237"/>
-      <c r="F7" s="237"/>
-      <c r="G7" s="237"/>
-      <c r="H7" s="237"/>
-      <c r="I7" s="237"/>
-      <c r="J7" s="237"/>
-      <c r="K7" s="237"/>
-      <c r="L7" s="237"/>
-      <c r="M7" s="237"/>
-      <c r="N7" s="237"/>
-      <c r="O7" s="237"/>
-      <c r="P7" s="238"/>
+    <row r="7" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="211"/>
+      <c r="B7" s="212"/>
+      <c r="C7" s="212"/>
+      <c r="D7" s="212"/>
+      <c r="E7" s="212"/>
+      <c r="F7" s="212"/>
+      <c r="G7" s="212"/>
+      <c r="H7" s="212"/>
+      <c r="I7" s="212"/>
+      <c r="J7" s="212"/>
+      <c r="K7" s="212"/>
+      <c r="L7" s="212"/>
+      <c r="M7" s="212"/>
+      <c r="N7" s="212"/>
+      <c r="O7" s="212"/>
+      <c r="P7" s="213"/>
       <c r="Q7" s="81"/>
     </row>
-    <row r="8" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="235"/>
-      <c r="B8" s="236"/>
-      <c r="C8" s="237"/>
-      <c r="D8" s="237"/>
-      <c r="E8" s="237"/>
-      <c r="F8" s="237"/>
-      <c r="G8" s="237"/>
-      <c r="H8" s="237"/>
-      <c r="I8" s="237"/>
-      <c r="J8" s="237"/>
-      <c r="K8" s="237"/>
-      <c r="L8" s="237"/>
-      <c r="M8" s="237"/>
-      <c r="N8" s="237"/>
-      <c r="O8" s="237"/>
-      <c r="P8" s="238"/>
+    <row r="8" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="211"/>
+      <c r="B8" s="212"/>
+      <c r="C8" s="212"/>
+      <c r="D8" s="212"/>
+      <c r="E8" s="212"/>
+      <c r="F8" s="212"/>
+      <c r="G8" s="212"/>
+      <c r="H8" s="212"/>
+      <c r="I8" s="212"/>
+      <c r="J8" s="212"/>
+      <c r="K8" s="212"/>
+      <c r="L8" s="212"/>
+      <c r="M8" s="212"/>
+      <c r="N8" s="212"/>
+      <c r="O8" s="212"/>
+      <c r="P8" s="213"/>
       <c r="Q8" s="81"/>
     </row>
-    <row r="9" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="235"/>
-      <c r="B9" s="236"/>
-      <c r="C9" s="237"/>
-      <c r="D9" s="237"/>
-      <c r="E9" s="237"/>
-      <c r="F9" s="237"/>
-      <c r="G9" s="237"/>
-      <c r="H9" s="237"/>
-      <c r="I9" s="237"/>
-      <c r="J9" s="237"/>
-      <c r="K9" s="237"/>
-      <c r="L9" s="237"/>
-      <c r="M9" s="237"/>
-      <c r="N9" s="237"/>
-      <c r="O9" s="237"/>
-      <c r="P9" s="238"/>
+    <row r="9" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="211"/>
+      <c r="B9" s="212"/>
+      <c r="C9" s="212"/>
+      <c r="D9" s="212"/>
+      <c r="E9" s="212"/>
+      <c r="F9" s="212"/>
+      <c r="G9" s="212"/>
+      <c r="H9" s="212"/>
+      <c r="I9" s="212"/>
+      <c r="J9" s="212"/>
+      <c r="K9" s="212"/>
+      <c r="L9" s="212"/>
+      <c r="M9" s="212"/>
+      <c r="N9" s="212"/>
+      <c r="O9" s="212"/>
+      <c r="P9" s="213"/>
       <c r="Q9" s="81"/>
     </row>
-    <row r="10" spans="1:18" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="239"/>
-      <c r="B10" s="240"/>
-      <c r="C10" s="240"/>
-      <c r="D10" s="240"/>
-      <c r="E10" s="240"/>
-      <c r="F10" s="240"/>
-      <c r="G10" s="240"/>
-      <c r="H10" s="240"/>
-      <c r="I10" s="240"/>
-      <c r="J10" s="240"/>
-      <c r="K10" s="240"/>
-      <c r="L10" s="240"/>
-      <c r="M10" s="240"/>
-      <c r="N10" s="240"/>
-      <c r="O10" s="240"/>
-      <c r="P10" s="241"/>
-    </row>
-    <row r="11" spans="1:18" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="248" t="s">
+    <row r="10" spans="1:18" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="214"/>
+      <c r="B10" s="215"/>
+      <c r="C10" s="215"/>
+      <c r="D10" s="215"/>
+      <c r="E10" s="215"/>
+      <c r="F10" s="215"/>
+      <c r="G10" s="215"/>
+      <c r="H10" s="215"/>
+      <c r="I10" s="215"/>
+      <c r="J10" s="215"/>
+      <c r="K10" s="215"/>
+      <c r="L10" s="215"/>
+      <c r="M10" s="215"/>
+      <c r="N10" s="215"/>
+      <c r="O10" s="215"/>
+      <c r="P10" s="216"/>
+    </row>
+    <row r="11" spans="1:18" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="223" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="249"/>
-      <c r="C11" s="249"/>
-      <c r="D11" s="249"/>
-      <c r="E11" s="249"/>
-      <c r="F11" s="249"/>
-      <c r="G11" s="249"/>
-      <c r="H11" s="249"/>
-      <c r="I11" s="249"/>
-      <c r="J11" s="249"/>
-      <c r="K11" s="249"/>
-      <c r="L11" s="249"/>
-      <c r="M11" s="249"/>
-      <c r="N11" s="249"/>
-      <c r="O11" s="249"/>
-      <c r="P11" s="250"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="242" t="s">
+      <c r="B11" s="224"/>
+      <c r="C11" s="224"/>
+      <c r="D11" s="224"/>
+      <c r="E11" s="224"/>
+      <c r="F11" s="224"/>
+      <c r="G11" s="224"/>
+      <c r="H11" s="224"/>
+      <c r="I11" s="224"/>
+      <c r="J11" s="224"/>
+      <c r="K11" s="224"/>
+      <c r="L11" s="224"/>
+      <c r="M11" s="224"/>
+      <c r="N11" s="224"/>
+      <c r="O11" s="224"/>
+      <c r="P11" s="225"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" s="217" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="220" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" s="244" t="s">
+      <c r="B12" s="228" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="219" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="244" t="s">
+      <c r="D12" s="219" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="244" t="s">
+      <c r="E12" s="219" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="218" t="s">
+      <c r="F12" s="201" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="244" t="s">
+      <c r="G12" s="219" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="246" t="s">
+      <c r="H12" s="221" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="218" t="s">
+      <c r="I12" s="201" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="218" t="s">
+      <c r="J12" s="201" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="218" t="s">
+      <c r="K12" s="201" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="220" t="s">
-        <v>230</v>
-      </c>
-      <c r="M12" s="218" t="s">
-        <v>227</v>
-      </c>
-      <c r="N12" s="252" t="s">
+      <c r="L12" s="228" t="s">
+        <v>213</v>
+      </c>
+      <c r="M12" s="201" t="s">
+        <v>210</v>
+      </c>
+      <c r="N12" s="226" t="s">
         <v>52</v>
       </c>
       <c r="O12" s="117" t="s">
         <v>36</v>
       </c>
-      <c r="P12" s="228" t="s">
+      <c r="P12" s="203" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="243"/>
-      <c r="B13" s="221"/>
-      <c r="C13" s="245"/>
-      <c r="D13" s="245"/>
-      <c r="E13" s="245"/>
-      <c r="F13" s="219"/>
-      <c r="G13" s="245"/>
-      <c r="H13" s="247"/>
-      <c r="I13" s="219"/>
-      <c r="J13" s="219"/>
-      <c r="K13" s="219"/>
-      <c r="L13" s="221"/>
-      <c r="M13" s="219"/>
-      <c r="N13" s="253"/>
+    <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="218"/>
+      <c r="B13" s="229"/>
+      <c r="C13" s="220"/>
+      <c r="D13" s="220"/>
+      <c r="E13" s="220"/>
+      <c r="F13" s="202"/>
+      <c r="G13" s="220"/>
+      <c r="H13" s="222"/>
+      <c r="I13" s="202"/>
+      <c r="J13" s="202"/>
+      <c r="K13" s="202"/>
+      <c r="L13" s="229"/>
+      <c r="M13" s="202"/>
+      <c r="N13" s="227"/>
       <c r="O13" s="118" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 18/06</v>
       </c>
-      <c r="P13" s="229"/>
-    </row>
-    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P13" s="204"/>
+    </row>
+    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="107">
         <v>1</v>
       </c>
-      <c r="B14" s="179" t="s">
-        <v>94</v>
+      <c r="B14" s="156" t="s">
+        <v>77</v>
       </c>
       <c r="C14" s="94" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="D14" s="94"/>
       <c r="E14" s="96">
@@ -4040,18 +3900,18 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="107">
         <v>2</v>
       </c>
-      <c r="B15" s="179" t="s">
-        <v>97</v>
+      <c r="B15" s="156" t="s">
+        <v>80</v>
       </c>
       <c r="C15" s="94" t="s">
-        <v>141</v>
-      </c>
-      <c r="D15" s="183" t="s">
-        <v>208</v>
+        <v>124</v>
+      </c>
+      <c r="D15" s="94" t="s">
+        <v>191</v>
       </c>
       <c r="E15" s="96">
         <v>3.4</v>
@@ -4100,18 +3960,18 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="107">
         <v>3</v>
       </c>
-      <c r="B16" s="179" t="s">
-        <v>98</v>
+      <c r="B16" s="156" t="s">
+        <v>81</v>
       </c>
       <c r="C16" s="94" t="s">
-        <v>142</v>
-      </c>
-      <c r="D16" s="183" t="s">
-        <v>213</v>
+        <v>125</v>
+      </c>
+      <c r="D16" s="94" t="s">
+        <v>196</v>
       </c>
       <c r="E16" s="96">
         <v>2.54</v>
@@ -4159,19 +4019,22 @@
         <f t="shared" ref="Q16:Q31" si="8">Q15+0.01</f>
         <v>0.03</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="107">
+      <c r="R16" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="176">
         <v>4</v>
       </c>
-      <c r="B17" s="179" t="s">
-        <v>99</v>
-      </c>
-      <c r="C17" s="94" t="s">
-        <v>143</v>
+      <c r="B17" s="177" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="179" t="s">
+        <v>126</v>
       </c>
       <c r="D17" s="99" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="E17" s="96">
         <v>5.19</v>
@@ -4220,19 +4083,22 @@
         <f t="shared" si="8"/>
         <v>0.04</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R17" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="107">
         <v>5</v>
       </c>
-      <c r="B18" s="179" t="s">
-        <v>95</v>
+      <c r="B18" s="156" t="s">
+        <v>78</v>
       </c>
       <c r="C18" s="94" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="D18" s="99" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="E18" s="96">
         <v>3.4</v>
@@ -4281,15 +4147,15 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="107">
         <v>6</v>
       </c>
-      <c r="B19" s="179" t="s">
-        <v>100</v>
+      <c r="B19" s="156" t="s">
+        <v>83</v>
       </c>
       <c r="C19" s="94" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="D19" s="94"/>
       <c r="E19" s="96">
@@ -4339,15 +4205,15 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="107">
         <v>7</v>
       </c>
-      <c r="B20" s="179" t="s">
-        <v>101</v>
+      <c r="B20" s="156" t="s">
+        <v>84</v>
       </c>
       <c r="C20" s="94" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="D20" s="94"/>
       <c r="E20" s="96">
@@ -4398,15 +4264,15 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="107">
         <v>8</v>
       </c>
-      <c r="B21" s="179" t="s">
-        <v>102</v>
+      <c r="B21" s="156" t="s">
+        <v>85</v>
       </c>
       <c r="C21" s="94" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="D21" s="99"/>
       <c r="E21" s="96">
@@ -4456,18 +4322,18 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="107">
         <v>9</v>
       </c>
-      <c r="B22" s="179" t="s">
-        <v>96</v>
+      <c r="B22" s="156" t="s">
+        <v>79</v>
       </c>
       <c r="C22" s="94" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="D22" s="99" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="E22" s="96">
         <v>2.54</v>
@@ -4516,15 +4382,15 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="107">
         <v>10</v>
       </c>
-      <c r="B23" s="179" t="s">
-        <v>103</v>
+      <c r="B23" s="156" t="s">
+        <v>86</v>
       </c>
       <c r="C23" s="94" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="D23" s="99"/>
       <c r="E23" s="96">
@@ -4575,18 +4441,18 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="107">
         <v>11</v>
       </c>
-      <c r="B24" s="179" t="s">
-        <v>104</v>
+      <c r="B24" s="156" t="s">
+        <v>87</v>
       </c>
       <c r="C24" s="94" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="D24" s="99" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="E24" s="96">
         <v>3.4</v>
@@ -4635,18 +4501,18 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="107">
         <v>12</v>
       </c>
-      <c r="B25" s="179" t="s">
-        <v>105</v>
+      <c r="B25" s="156" t="s">
+        <v>88</v>
       </c>
       <c r="C25" s="94" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="D25" s="99" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="E25" s="96">
         <v>2.54</v>
@@ -4696,15 +4562,15 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="107">
         <v>13</v>
       </c>
-      <c r="B26" s="179" t="s">
-        <v>106</v>
+      <c r="B26" s="156" t="s">
+        <v>89</v>
       </c>
       <c r="C26" s="94" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="D26" s="99"/>
       <c r="E26" s="96">
@@ -4755,15 +4621,15 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="107">
         <v>14</v>
       </c>
-      <c r="B27" s="179" t="s">
-        <v>107</v>
+      <c r="B27" s="156" t="s">
+        <v>90</v>
       </c>
       <c r="C27" s="94" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="D27" s="99"/>
       <c r="E27" s="96">
@@ -4814,18 +4680,18 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="107">
         <v>15</v>
       </c>
-      <c r="B28" s="179" t="s">
-        <v>108</v>
+      <c r="B28" s="156" t="s">
+        <v>91</v>
       </c>
       <c r="C28" s="94" t="s">
-        <v>152</v>
-      </c>
-      <c r="D28" s="183" t="s">
-        <v>204</v>
+        <v>135</v>
+      </c>
+      <c r="D28" s="94" t="s">
+        <v>187</v>
       </c>
       <c r="E28" s="96">
         <v>2.54</v>
@@ -4874,15 +4740,15 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="107">
         <v>16</v>
       </c>
-      <c r="B29" s="179" t="s">
-        <v>109</v>
+      <c r="B29" s="156" t="s">
+        <v>92</v>
       </c>
       <c r="C29" s="94" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="D29" s="94"/>
       <c r="E29" s="96">
@@ -4933,18 +4799,18 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="107">
         <v>17</v>
       </c>
-      <c r="B30" s="179" t="s">
-        <v>110</v>
+      <c r="B30" s="156" t="s">
+        <v>93</v>
       </c>
       <c r="C30" s="94" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="D30" s="99" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="E30" s="96">
         <v>3.4</v>
@@ -4994,15 +4860,15 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="107">
         <v>18</v>
       </c>
-      <c r="B31" s="179" t="s">
-        <v>111</v>
+      <c r="B31" s="156" t="s">
+        <v>94</v>
       </c>
       <c r="C31" s="94" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="D31" s="95"/>
       <c r="E31" s="96">
@@ -5050,15 +4916,15 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="107">
         <v>19</v>
       </c>
-      <c r="B32" s="179" t="s">
-        <v>112</v>
+      <c r="B32" s="156" t="s">
+        <v>95</v>
       </c>
       <c r="C32" s="94" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="D32" s="99"/>
       <c r="E32" s="96">
@@ -5108,15 +4974,15 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" s="107">
         <v>20</v>
       </c>
-      <c r="B33" s="179" t="s">
-        <v>113</v>
+      <c r="B33" s="156" t="s">
+        <v>96</v>
       </c>
       <c r="C33" s="94" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="D33" s="99"/>
       <c r="E33" s="96">
@@ -5164,18 +5030,18 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="107">
         <v>21</v>
       </c>
-      <c r="B34" s="179" t="s">
-        <v>114</v>
+      <c r="B34" s="156" t="s">
+        <v>97</v>
       </c>
       <c r="C34" s="100" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="D34" s="99" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="E34" s="96">
         <v>2.54</v>
@@ -5224,19 +5090,19 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A35" s="107">
         <f>A34+1</f>
         <v>22</v>
       </c>
-      <c r="B35" s="179" t="s">
-        <v>115</v>
+      <c r="B35" s="156" t="s">
+        <v>98</v>
       </c>
       <c r="C35" s="100" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="D35" s="99" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="E35" s="96">
         <v>4.9400000000000004</v>
@@ -5286,19 +5152,19 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" s="107">
         <f t="shared" ref="A36:A59" si="11">A35+1</f>
         <v>23</v>
       </c>
-      <c r="B36" s="179" t="s">
-        <v>116</v>
+      <c r="B36" s="156" t="s">
+        <v>99</v>
       </c>
       <c r="C36" s="100" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="D36" s="99" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="E36" s="96">
         <v>3.28</v>
@@ -5347,16 +5213,16 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" s="107">
         <f t="shared" si="11"/>
         <v>24</v>
       </c>
-      <c r="B37" s="179" t="s">
-        <v>117</v>
+      <c r="B37" s="156" t="s">
+        <v>100</v>
       </c>
       <c r="C37" s="100" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="D37" s="99"/>
       <c r="E37" s="96">
@@ -5406,16 +5272,16 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="107">
         <f t="shared" si="11"/>
         <v>25</v>
       </c>
-      <c r="B38" s="179" t="s">
-        <v>118</v>
+      <c r="B38" s="156" t="s">
+        <v>101</v>
       </c>
       <c r="C38" s="100" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="D38" s="99"/>
       <c r="E38" s="96">
@@ -5466,19 +5332,19 @@
         <v>0.25000000000000006</v>
       </c>
       <c r="R38" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" s="107">
         <f t="shared" si="11"/>
         <v>26</v>
       </c>
-      <c r="B39" s="179" t="s">
-        <v>120</v>
+      <c r="B39" s="156" t="s">
+        <v>103</v>
       </c>
       <c r="C39" s="100" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="D39" s="99"/>
       <c r="E39" s="96">
@@ -5528,16 +5394,16 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" s="107">
         <f t="shared" si="11"/>
         <v>27</v>
       </c>
-      <c r="B40" s="179" t="s">
-        <v>119</v>
+      <c r="B40" s="156" t="s">
+        <v>102</v>
       </c>
       <c r="C40" s="100" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="D40" s="99"/>
       <c r="E40" s="96">
@@ -5588,19 +5454,19 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" s="107">
         <f t="shared" si="11"/>
         <v>28</v>
       </c>
-      <c r="B41" s="179" t="s">
-        <v>121</v>
+      <c r="B41" s="156" t="s">
+        <v>104</v>
       </c>
       <c r="C41" s="100" t="s">
-        <v>161</v>
-      </c>
-      <c r="D41" s="183" t="s">
-        <v>208</v>
+        <v>144</v>
+      </c>
+      <c r="D41" s="94" t="s">
+        <v>191</v>
       </c>
       <c r="E41" s="96">
         <v>0.28999999999999998</v>
@@ -5649,19 +5515,19 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" s="107">
         <f t="shared" si="11"/>
         <v>29</v>
       </c>
-      <c r="B42" s="179" t="s">
-        <v>122</v>
+      <c r="B42" s="156" t="s">
+        <v>105</v>
       </c>
       <c r="C42" s="100" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="D42" s="99" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="E42" s="96">
         <v>0.08</v>
@@ -5711,16 +5577,16 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" s="107">
         <f t="shared" si="11"/>
         <v>30</v>
       </c>
-      <c r="B43" s="179" t="s">
+      <c r="B43" s="156" t="s">
+        <v>106</v>
+      </c>
+      <c r="C43" s="100" t="s">
         <v>123</v>
-      </c>
-      <c r="C43" s="100" t="s">
-        <v>140</v>
       </c>
       <c r="D43" s="99"/>
       <c r="E43" s="96">
@@ -5770,16 +5636,16 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A44" s="107">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A44" s="176">
         <f t="shared" si="11"/>
         <v>31</v>
       </c>
-      <c r="B44" s="179" t="s">
-        <v>124</v>
-      </c>
-      <c r="C44" s="100" t="s">
-        <v>143</v>
+      <c r="B44" s="177" t="s">
+        <v>107</v>
+      </c>
+      <c r="C44" s="178" t="s">
+        <v>126</v>
       </c>
       <c r="D44" s="99"/>
       <c r="E44" s="96">
@@ -5826,17 +5692,20 @@
         <f t="shared" si="9"/>
         <v>0.31000000000000011</v>
       </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R44" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" s="107">
         <f t="shared" si="11"/>
         <v>32</v>
       </c>
-      <c r="B45" s="179" t="s">
-        <v>125</v>
+      <c r="B45" s="156" t="s">
+        <v>108</v>
       </c>
       <c r="C45" s="100" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="D45" s="99"/>
       <c r="E45" s="96">
@@ -5886,16 +5755,16 @@
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" s="107">
         <f t="shared" si="11"/>
         <v>33</v>
       </c>
-      <c r="B46" s="179" t="s">
-        <v>126</v>
+      <c r="B46" s="156" t="s">
+        <v>109</v>
       </c>
       <c r="C46" s="100" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="D46" s="99"/>
       <c r="E46" s="96">
@@ -5940,16 +5809,16 @@
         <v>0.33000000000000013</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" s="107">
         <f t="shared" si="11"/>
         <v>34</v>
       </c>
-      <c r="B47" s="179" t="s">
-        <v>127</v>
+      <c r="B47" s="156" t="s">
+        <v>110</v>
       </c>
       <c r="C47" s="100" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="D47" s="99"/>
       <c r="E47" s="96">
@@ -5999,30 +5868,30 @@
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A48" s="170">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A48" s="147">
         <f t="shared" si="11"/>
         <v>35</v>
       </c>
-      <c r="B48" s="179" t="s">
-        <v>128</v>
-      </c>
-      <c r="C48" s="171" t="s">
-        <v>163</v>
-      </c>
-      <c r="D48" s="172"/>
-      <c r="E48" s="173">
+      <c r="B48" s="156" t="s">
+        <v>111</v>
+      </c>
+      <c r="C48" s="148" t="s">
+        <v>146</v>
+      </c>
+      <c r="D48" s="149"/>
+      <c r="E48" s="150">
         <v>0.09</v>
       </c>
       <c r="F48" s="82">
         <v>6231</v>
       </c>
       <c r="G48" s="82"/>
-      <c r="H48" s="174">
+      <c r="H48" s="151">
         <f t="shared" si="0"/>
         <v>6231</v>
       </c>
-      <c r="I48" s="174">
+      <c r="I48" s="151">
         <f t="shared" si="3"/>
         <v>186.93</v>
       </c>
@@ -6030,7 +5899,7 @@
         <f t="shared" si="4"/>
         <v>5687.549532</v>
       </c>
-      <c r="K48" s="175">
+      <c r="K48" s="152">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -6042,7 +5911,7 @@
         <f t="shared" si="6"/>
         <v>897.90975899999989</v>
       </c>
-      <c r="N48" s="175"/>
+      <c r="N48" s="152"/>
       <c r="O48" s="98">
         <f t="shared" si="7"/>
         <v>13168.35</v>
@@ -6056,16 +5925,16 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" s="107">
         <f t="shared" si="11"/>
         <v>36</v>
       </c>
-      <c r="B49" s="179" t="s">
-        <v>129</v>
+      <c r="B49" s="156" t="s">
+        <v>112</v>
       </c>
       <c r="C49" s="100" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="D49" s="99"/>
       <c r="E49" s="96">
@@ -6115,16 +5984,16 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" s="107">
         <f t="shared" si="11"/>
         <v>37</v>
       </c>
-      <c r="B50" s="179" t="s">
-        <v>130</v>
+      <c r="B50" s="156" t="s">
+        <v>113</v>
       </c>
       <c r="C50" s="100" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="D50" s="99"/>
       <c r="E50" s="96">
@@ -6172,16 +6041,16 @@
         <v>0.37000000000000016</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" s="107">
         <f t="shared" si="11"/>
         <v>38</v>
       </c>
-      <c r="B51" s="179" t="s">
-        <v>131</v>
+      <c r="B51" s="156" t="s">
+        <v>114</v>
       </c>
       <c r="C51" s="100" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="D51" s="99"/>
       <c r="E51" s="96">
@@ -6231,16 +6100,16 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" s="107">
         <f t="shared" si="11"/>
         <v>39</v>
       </c>
-      <c r="B52" s="179" t="s">
-        <v>132</v>
+      <c r="B52" s="156" t="s">
+        <v>115</v>
       </c>
       <c r="C52" s="100" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="D52" s="99"/>
       <c r="E52" s="96">
@@ -6290,22 +6159,22 @@
         <v>0.39000000000000018</v>
       </c>
       <c r="R52" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" s="107">
         <f t="shared" si="11"/>
         <v>40</v>
       </c>
-      <c r="B53" s="179" t="s">
-        <v>133</v>
+      <c r="B53" s="156" t="s">
+        <v>116</v>
       </c>
       <c r="C53" s="100" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="D53" s="99" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="E53" s="96">
         <v>0.77</v>
@@ -6355,19 +6224,19 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" s="107">
         <f t="shared" si="11"/>
         <v>41</v>
       </c>
-      <c r="B54" s="179" t="s">
-        <v>134</v>
+      <c r="B54" s="156" t="s">
+        <v>117</v>
       </c>
       <c r="C54" s="100" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="D54" s="99" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="E54" s="96">
         <v>0.81</v>
@@ -6416,19 +6285,19 @@
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A55" s="107">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A55" s="176">
         <f t="shared" si="11"/>
         <v>42</v>
       </c>
-      <c r="B55" s="179" t="s">
-        <v>135</v>
-      </c>
-      <c r="C55" s="100" t="s">
-        <v>165</v>
+      <c r="B55" s="177" t="s">
+        <v>118</v>
+      </c>
+      <c r="C55" s="178" t="s">
+        <v>148</v>
       </c>
       <c r="D55" s="99" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="E55" s="96">
         <v>0.77</v>
@@ -6473,17 +6342,20 @@
         <f t="shared" si="9"/>
         <v>0.42000000000000021</v>
       </c>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R55" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" s="107">
         <f t="shared" si="11"/>
         <v>43</v>
       </c>
-      <c r="B56" s="179" t="s">
-        <v>136</v>
+      <c r="B56" s="156" t="s">
+        <v>119</v>
       </c>
       <c r="C56" s="100" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="D56" s="99"/>
       <c r="E56" s="96">
@@ -6531,16 +6403,16 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" s="107">
         <f t="shared" si="11"/>
         <v>44</v>
       </c>
-      <c r="B57" s="179" t="s">
-        <v>137</v>
+      <c r="B57" s="156" t="s">
+        <v>120</v>
       </c>
       <c r="C57" s="100" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="D57" s="99"/>
       <c r="E57" s="96">
@@ -6588,19 +6460,19 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" s="107">
         <f t="shared" si="11"/>
         <v>45</v>
       </c>
-      <c r="B58" s="179" t="s">
-        <v>138</v>
+      <c r="B58" s="156" t="s">
+        <v>121</v>
       </c>
       <c r="C58" s="100" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="D58" s="99" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="E58" s="96">
         <v>0.77</v>
@@ -6650,16 +6522,16 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" s="107">
         <f t="shared" si="11"/>
         <v>46</v>
       </c>
-      <c r="B59" s="179" t="s">
-        <v>139</v>
+      <c r="B59" s="156" t="s">
+        <v>122</v>
       </c>
       <c r="C59" s="100" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="D59" s="99"/>
       <c r="E59" s="96">
@@ -6709,12 +6581,12 @@
         <v>0.46000000000000024</v>
       </c>
       <c r="R59" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" s="107"/>
-      <c r="B60" s="179"/>
+      <c r="B60" s="156"/>
       <c r="C60" s="94"/>
       <c r="D60" s="99"/>
       <c r="E60" s="96"/>
@@ -6731,9 +6603,9 @@
       <c r="P60" s="115"/>
       <c r="Q60" s="51"/>
     </row>
-    <row r="61" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="108"/>
-      <c r="B61" s="180"/>
+      <c r="B61" s="157"/>
       <c r="C61" s="109"/>
       <c r="D61" s="109"/>
       <c r="E61" s="110">
@@ -6782,105 +6654,113 @@
         <v>9920424.8099999987</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C62" s="83"/>
       <c r="D62" s="83"/>
     </row>
-    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C64" s="230" t="s">
+    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C64" s="206" t="s">
         <v>6</v>
       </c>
-      <c r="D64" s="230"/>
-      <c r="E64" s="230"/>
-      <c r="F64" s="230"/>
-      <c r="G64" s="230"/>
-      <c r="H64" s="230"/>
-      <c r="I64" s="230"/>
-      <c r="J64" s="230"/>
-      <c r="K64" s="230"/>
-      <c r="L64" s="230"/>
-      <c r="M64" s="230"/>
-      <c r="N64" s="230"/>
-      <c r="O64" s="230"/>
-    </row>
-    <row r="65" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C65" s="230"/>
-      <c r="D65" s="230"/>
-      <c r="E65" s="230"/>
-      <c r="F65" s="230"/>
-      <c r="G65" s="230"/>
-      <c r="H65" s="230"/>
-      <c r="I65" s="230"/>
-      <c r="J65" s="230"/>
-      <c r="K65" s="230"/>
-      <c r="L65" s="230"/>
-      <c r="M65" s="230"/>
-      <c r="N65" s="230"/>
-      <c r="O65" s="230"/>
-    </row>
-    <row r="66" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C66" s="230"/>
-      <c r="D66" s="230"/>
-      <c r="E66" s="230"/>
-      <c r="F66" s="230"/>
-      <c r="G66" s="230"/>
-      <c r="H66" s="230"/>
-      <c r="I66" s="230"/>
-      <c r="J66" s="230"/>
-      <c r="K66" s="230"/>
-      <c r="L66" s="230"/>
-      <c r="M66" s="230"/>
-      <c r="N66" s="230"/>
-      <c r="O66" s="230"/>
-    </row>
-    <row r="67" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C67" s="230"/>
-      <c r="D67" s="230"/>
-      <c r="E67" s="230"/>
-      <c r="F67" s="230"/>
-      <c r="G67" s="230"/>
-      <c r="H67" s="230"/>
-      <c r="I67" s="230"/>
-      <c r="J67" s="230"/>
-      <c r="K67" s="230"/>
-      <c r="L67" s="230"/>
-      <c r="M67" s="230"/>
-      <c r="N67" s="230"/>
-      <c r="O67" s="230"/>
-    </row>
-    <row r="68" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C68" s="230"/>
-      <c r="D68" s="230"/>
-      <c r="E68" s="230"/>
-      <c r="F68" s="230"/>
-      <c r="G68" s="230"/>
-      <c r="H68" s="230"/>
-      <c r="I68" s="230"/>
-      <c r="J68" s="230"/>
-      <c r="K68" s="230"/>
-      <c r="L68" s="230"/>
-      <c r="M68" s="230"/>
-      <c r="N68" s="230"/>
-      <c r="O68" s="230"/>
-    </row>
-    <row r="69" spans="3:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C69" s="230"/>
-      <c r="D69" s="230"/>
-      <c r="E69" s="230"/>
-      <c r="F69" s="230"/>
-      <c r="G69" s="230"/>
-      <c r="H69" s="230"/>
-      <c r="I69" s="230"/>
-      <c r="J69" s="230"/>
-      <c r="K69" s="230"/>
-      <c r="L69" s="230"/>
-      <c r="M69" s="230"/>
-      <c r="N69" s="230"/>
-      <c r="O69" s="230"/>
+      <c r="D64" s="206"/>
+      <c r="E64" s="206"/>
+      <c r="F64" s="206"/>
+      <c r="G64" s="206"/>
+      <c r="H64" s="206"/>
+      <c r="I64" s="206"/>
+      <c r="J64" s="206"/>
+      <c r="K64" s="206"/>
+      <c r="L64" s="206"/>
+      <c r="M64" s="206"/>
+      <c r="N64" s="206"/>
+      <c r="O64" s="206"/>
+    </row>
+    <row r="65" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C65" s="206"/>
+      <c r="D65" s="206"/>
+      <c r="E65" s="206"/>
+      <c r="F65" s="206"/>
+      <c r="G65" s="206"/>
+      <c r="H65" s="206"/>
+      <c r="I65" s="206"/>
+      <c r="J65" s="206"/>
+      <c r="K65" s="206"/>
+      <c r="L65" s="206"/>
+      <c r="M65" s="206"/>
+      <c r="N65" s="206"/>
+      <c r="O65" s="206"/>
+    </row>
+    <row r="66" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C66" s="206"/>
+      <c r="D66" s="206"/>
+      <c r="E66" s="206"/>
+      <c r="F66" s="206"/>
+      <c r="G66" s="206"/>
+      <c r="H66" s="206"/>
+      <c r="I66" s="206"/>
+      <c r="J66" s="206"/>
+      <c r="K66" s="206"/>
+      <c r="L66" s="206"/>
+      <c r="M66" s="206"/>
+      <c r="N66" s="206"/>
+      <c r="O66" s="206"/>
+    </row>
+    <row r="67" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C67" s="206"/>
+      <c r="D67" s="206"/>
+      <c r="E67" s="206"/>
+      <c r="F67" s="206"/>
+      <c r="G67" s="206"/>
+      <c r="H67" s="206"/>
+      <c r="I67" s="206"/>
+      <c r="J67" s="206"/>
+      <c r="K67" s="206"/>
+      <c r="L67" s="206"/>
+      <c r="M67" s="206"/>
+      <c r="N67" s="206"/>
+      <c r="O67" s="206"/>
+    </row>
+    <row r="68" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C68" s="206"/>
+      <c r="D68" s="206"/>
+      <c r="E68" s="206"/>
+      <c r="F68" s="206"/>
+      <c r="G68" s="206"/>
+      <c r="H68" s="206"/>
+      <c r="I68" s="206"/>
+      <c r="J68" s="206"/>
+      <c r="K68" s="206"/>
+      <c r="L68" s="206"/>
+      <c r="M68" s="206"/>
+      <c r="N68" s="206"/>
+      <c r="O68" s="206"/>
+    </row>
+    <row r="69" spans="3:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C69" s="206"/>
+      <c r="D69" s="206"/>
+      <c r="E69" s="206"/>
+      <c r="F69" s="206"/>
+      <c r="G69" s="206"/>
+      <c r="H69" s="206"/>
+      <c r="I69" s="206"/>
+      <c r="J69" s="206"/>
+      <c r="K69" s="206"/>
+      <c r="L69" s="206"/>
+      <c r="M69" s="206"/>
+      <c r="N69" s="206"/>
+      <c r="O69" s="206"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="J1:P5"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="P12:P13"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="C64:O69"/>
     <mergeCell ref="A6:P10"/>
     <mergeCell ref="A12:A13"/>
@@ -6893,14 +6773,6 @@
     <mergeCell ref="I12:I13"/>
     <mergeCell ref="A11:P11"/>
     <mergeCell ref="J12:J13"/>
-    <mergeCell ref="N12:N13"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="J1:P5"/>
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="P12:P13"/>
-    <mergeCell ref="F2:G2"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -6910,17 +6782,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
-  <dimension ref="A3:L49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="C3:L9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C3" s="21"/>
     </row>
-    <row r="4" spans="1:12" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="141" t="s">
         <v>54</v>
       </c>
@@ -6933,10 +6805,10 @@
       <c r="H4" s="138"/>
       <c r="I4" s="138"/>
       <c r="J4" s="139"/>
-      <c r="K4" s="166"/>
-      <c r="L4" s="166"/>
-    </row>
-    <row r="5" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+    </row>
+    <row r="5" spans="3:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="143" t="s">
         <v>55</v>
       </c>
@@ -6948,525 +6820,68 @@
         <v>57</v>
       </c>
       <c r="H5" t="s">
+        <v>216</v>
+      </c>
+      <c r="J5" s="140"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
+    </row>
+    <row r="6" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C6" s="143" t="s">
         <v>58</v>
       </c>
-      <c r="J5" s="140"/>
-      <c r="K5" s="166"/>
-      <c r="L5" s="166"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C6" s="143" t="s">
+      <c r="D6" s="144" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="144" t="s">
+      <c r="E6" t="s">
         <v>60</v>
-      </c>
-      <c r="E6" t="s">
-        <v>61</v>
       </c>
       <c r="G6" t="s">
         <v>28</v>
       </c>
-      <c r="H6">
-        <v>71</v>
+      <c r="H6" t="s">
+        <v>215</v>
       </c>
       <c r="J6" s="140"/>
-      <c r="K6" s="166"/>
-      <c r="L6" s="166"/>
-    </row>
-    <row r="7" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
+    </row>
+    <row r="7" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C7" s="48" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J7" s="140"/>
-      <c r="K7" s="166"/>
-      <c r="L7" s="166"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C8" s="254" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="255"/>
-      <c r="E8" s="255"/>
-      <c r="F8" s="255"/>
-      <c r="G8" s="255"/>
-      <c r="H8" s="255"/>
-      <c r="I8" s="255"/>
-      <c r="J8" s="256"/>
-      <c r="K8" s="166"/>
-      <c r="L8" s="166"/>
-    </row>
-    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="257"/>
-      <c r="D9" s="258"/>
-      <c r="E9" s="258"/>
-      <c r="F9" s="258"/>
-      <c r="G9" s="258"/>
-      <c r="H9" s="258"/>
-      <c r="I9" s="258"/>
-      <c r="J9" s="259"/>
-    </row>
-    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="145"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C12" s="146" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="147">
-        <f>D4+1</f>
-        <v>2</v>
-      </c>
-      <c r="E12" s="138"/>
-      <c r="F12" s="138"/>
-      <c r="G12" s="138"/>
-      <c r="H12" s="138"/>
-      <c r="I12" s="138"/>
-      <c r="J12" s="139"/>
-      <c r="K12" s="166"/>
-      <c r="L12" s="166"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C13" s="148" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="149"/>
-      <c r="E13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13" t="s">
-        <v>57</v>
-      </c>
-      <c r="H13" t="s">
-        <v>58</v>
-      </c>
-      <c r="J13" s="140"/>
-      <c r="K13" s="166"/>
-      <c r="L13" s="166"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C14" s="148" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" s="149" t="s">
-        <v>60</v>
-      </c>
-      <c r="E14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14" t="s">
-        <v>28</v>
-      </c>
-      <c r="H14" t="s">
-        <v>65</v>
-      </c>
-      <c r="J14" s="140"/>
-      <c r="K14" s="166"/>
-      <c r="L14" s="166"/>
-    </row>
-    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="48" t="s">
-        <v>62</v>
-      </c>
-      <c r="J15" s="140"/>
-      <c r="K15" s="166"/>
-      <c r="L15" s="166"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C16" s="254" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" s="255"/>
-      <c r="E16" s="255"/>
-      <c r="F16" s="255"/>
-      <c r="G16" s="255"/>
-      <c r="H16" s="255"/>
-      <c r="I16" s="255"/>
-      <c r="J16" s="256"/>
-      <c r="K16" s="166"/>
-      <c r="L16" s="166"/>
-    </row>
-    <row r="17" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="257"/>
-      <c r="D17" s="258"/>
-      <c r="E17" s="258"/>
-      <c r="F17" s="258"/>
-      <c r="G17" s="258"/>
-      <c r="H17" s="258"/>
-      <c r="I17" s="258"/>
-      <c r="J17" s="259"/>
-    </row>
-    <row r="19" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C20" s="151" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" s="152">
-        <f>D12+1</f>
-        <v>3</v>
-      </c>
-      <c r="E20" s="138"/>
-      <c r="F20" s="138"/>
-      <c r="G20" s="138"/>
-      <c r="H20" s="138"/>
-      <c r="I20" s="138"/>
-      <c r="J20" s="139"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C21" s="153" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21" s="154"/>
-      <c r="E21" t="s">
-        <v>56</v>
-      </c>
-      <c r="G21" t="s">
-        <v>57</v>
-      </c>
-      <c r="H21" t="s">
-        <v>67</v>
-      </c>
-      <c r="I21" s="150" t="s">
-        <v>66</v>
-      </c>
-      <c r="J21" s="140"/>
-      <c r="K21" s="166"/>
-      <c r="L21" s="166"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C22" s="153" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" s="154" t="s">
-        <v>60</v>
-      </c>
-      <c r="E22" t="s">
-        <v>61</v>
-      </c>
-      <c r="G22" t="s">
-        <v>28</v>
-      </c>
-      <c r="H22" t="s">
-        <v>69</v>
-      </c>
-      <c r="J22" s="140"/>
-      <c r="K22" s="166"/>
-      <c r="L22" s="166"/>
-    </row>
-    <row r="23" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="48" t="s">
-        <v>62</v>
-      </c>
-      <c r="J23" s="140"/>
-      <c r="K23" s="166"/>
-      <c r="L23" s="166"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C24" s="254" t="s">
-        <v>68</v>
-      </c>
-      <c r="D24" s="255"/>
-      <c r="E24" s="255"/>
-      <c r="F24" s="255"/>
-      <c r="G24" s="255"/>
-      <c r="H24" s="255"/>
-      <c r="I24" s="255"/>
-      <c r="J24" s="256"/>
-      <c r="K24" s="166"/>
-      <c r="L24" s="166"/>
-    </row>
-    <row r="25" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="257"/>
-      <c r="D25" s="258"/>
-      <c r="E25" s="258"/>
-      <c r="F25" s="258"/>
-      <c r="G25" s="258"/>
-      <c r="H25" s="258"/>
-      <c r="I25" s="258"/>
-      <c r="J25" s="259"/>
-      <c r="K25" s="166"/>
-      <c r="L25" s="166"/>
-    </row>
-    <row r="27" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C28" s="155" t="s">
-        <v>54</v>
-      </c>
-      <c r="D28" s="15">
-        <f>D20+1</f>
-        <v>4</v>
-      </c>
-      <c r="E28" s="138"/>
-      <c r="F28" s="138"/>
-      <c r="G28" s="138"/>
-      <c r="H28" s="138"/>
-      <c r="I28" s="138"/>
-      <c r="J28" s="139"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C29" s="156" t="s">
-        <v>55</v>
-      </c>
-      <c r="D29" s="157"/>
-      <c r="E29" t="s">
-        <v>56</v>
-      </c>
-      <c r="G29" t="s">
-        <v>57</v>
-      </c>
-      <c r="H29" t="s">
-        <v>70</v>
-      </c>
-      <c r="I29" s="150"/>
-      <c r="J29" s="140"/>
-      <c r="K29" s="166"/>
-      <c r="L29" s="166"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C30" s="156" t="s">
-        <v>59</v>
-      </c>
-      <c r="D30" s="157" t="s">
-        <v>60</v>
-      </c>
-      <c r="E30" t="s">
-        <v>61</v>
-      </c>
-      <c r="G30" t="s">
-        <v>28</v>
-      </c>
-      <c r="H30">
-        <v>46</v>
-      </c>
-      <c r="I30" t="s">
-        <v>72</v>
-      </c>
-      <c r="J30" s="140"/>
-      <c r="K30" s="166"/>
-      <c r="L30" s="166"/>
-    </row>
-    <row r="31" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C31" s="48" t="s">
-        <v>62</v>
-      </c>
-      <c r="J31" s="140"/>
-      <c r="K31" s="166"/>
-      <c r="L31" s="166"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C32" s="254" t="s">
-        <v>71</v>
-      </c>
-      <c r="D32" s="255"/>
-      <c r="E32" s="255"/>
-      <c r="F32" s="255"/>
-      <c r="G32" s="255"/>
-      <c r="H32" s="255"/>
-      <c r="I32" s="255"/>
-      <c r="J32" s="256"/>
-      <c r="K32" s="166"/>
-      <c r="L32" s="166"/>
-    </row>
-    <row r="33" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="257"/>
-      <c r="D33" s="258"/>
-      <c r="E33" s="258"/>
-      <c r="F33" s="258"/>
-      <c r="G33" s="258"/>
-      <c r="H33" s="258"/>
-      <c r="I33" s="258"/>
-      <c r="J33" s="259"/>
-    </row>
-    <row r="35" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="36" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C36" s="158" t="s">
-        <v>54</v>
-      </c>
-      <c r="D36" s="159">
-        <f>D28+1</f>
-        <v>5</v>
-      </c>
-      <c r="E36" s="138"/>
-      <c r="F36" s="138"/>
-      <c r="G36" s="138"/>
-      <c r="H36" s="138"/>
-      <c r="I36" s="138"/>
-      <c r="J36" s="139"/>
-      <c r="K36" s="166"/>
-      <c r="L36" s="166"/>
-    </row>
-    <row r="37" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C37" s="160" t="s">
-        <v>55</v>
-      </c>
-      <c r="D37" s="161"/>
-      <c r="E37" t="s">
-        <v>56</v>
-      </c>
-      <c r="G37" t="s">
-        <v>57</v>
-      </c>
-      <c r="H37" t="s">
-        <v>73</v>
-      </c>
-      <c r="I37" s="150"/>
-      <c r="J37" s="140"/>
-      <c r="K37" s="166"/>
-      <c r="L37" s="166"/>
-    </row>
-    <row r="38" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C38" s="160" t="s">
-        <v>59</v>
-      </c>
-      <c r="D38" s="161" t="s">
-        <v>60</v>
-      </c>
-      <c r="E38" t="s">
-        <v>61</v>
-      </c>
-      <c r="G38" t="s">
-        <v>28</v>
-      </c>
-      <c r="H38" t="s">
-        <v>74</v>
-      </c>
-      <c r="J38" s="140"/>
-      <c r="K38" s="166"/>
-      <c r="L38" s="166"/>
-    </row>
-    <row r="39" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="48" t="s">
-        <v>62</v>
-      </c>
-      <c r="J39" s="140"/>
-      <c r="K39" s="166"/>
-      <c r="L39" s="166"/>
-    </row>
-    <row r="40" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C40" s="254" t="s">
-        <v>80</v>
-      </c>
-      <c r="D40" s="255"/>
-      <c r="E40" s="255"/>
-      <c r="F40" s="255"/>
-      <c r="G40" s="255"/>
-      <c r="H40" s="255"/>
-      <c r="I40" s="255"/>
-      <c r="J40" s="256"/>
-      <c r="K40" s="166"/>
-      <c r="L40" s="166"/>
-    </row>
-    <row r="41" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="257"/>
-      <c r="D41" s="258"/>
-      <c r="E41" s="258"/>
-      <c r="F41" s="258"/>
-      <c r="G41" s="258"/>
-      <c r="H41" s="258"/>
-      <c r="I41" s="258"/>
-      <c r="J41" s="259"/>
-    </row>
-    <row r="43" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="44" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C44" s="162" t="s">
-        <v>54</v>
-      </c>
-      <c r="D44" s="163">
-        <f>D36+1</f>
-        <v>6</v>
-      </c>
-      <c r="E44" s="138"/>
-      <c r="F44" s="138"/>
-      <c r="G44" s="138"/>
-      <c r="H44" s="138"/>
-      <c r="I44" s="138"/>
-      <c r="J44" s="139"/>
-    </row>
-    <row r="45" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C45" s="164" t="s">
-        <v>55</v>
-      </c>
-      <c r="D45" s="165"/>
-      <c r="E45" t="s">
-        <v>56</v>
-      </c>
-      <c r="G45" t="s">
-        <v>57</v>
-      </c>
-      <c r="H45" t="s">
-        <v>78</v>
-      </c>
-      <c r="I45" s="150"/>
-      <c r="J45" s="140"/>
-      <c r="K45" s="166"/>
-      <c r="L45" s="166"/>
-    </row>
-    <row r="46" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C46" s="164" t="s">
-        <v>59</v>
-      </c>
-      <c r="D46" s="165" t="s">
-        <v>60</v>
-      </c>
-      <c r="E46" t="s">
-        <v>61</v>
-      </c>
-      <c r="G46" t="s">
-        <v>28</v>
-      </c>
-      <c r="H46" t="s">
-        <v>77</v>
-      </c>
-      <c r="J46" s="140"/>
-      <c r="K46" s="166"/>
-      <c r="L46" s="166"/>
-    </row>
-    <row r="47" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C47" s="48" t="s">
-        <v>62</v>
-      </c>
-      <c r="J47" s="140"/>
-      <c r="K47" s="166"/>
-      <c r="L47" s="166"/>
-    </row>
-    <row r="48" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C48" s="254" t="s">
-        <v>79</v>
-      </c>
-      <c r="D48" s="255"/>
-      <c r="E48" s="255"/>
-      <c r="F48" s="255"/>
-      <c r="G48" s="255"/>
-      <c r="H48" s="255"/>
-      <c r="I48" s="255"/>
-      <c r="J48" s="256"/>
-      <c r="K48" s="166"/>
-      <c r="L48" s="166"/>
-    </row>
-    <row r="49" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C49" s="257"/>
-      <c r="D49" s="258"/>
-      <c r="E49" s="258"/>
-      <c r="F49" s="258"/>
-      <c r="G49" s="258"/>
-      <c r="H49" s="258"/>
-      <c r="I49" s="258"/>
-      <c r="J49" s="259"/>
-      <c r="K49" s="166"/>
-      <c r="L49" s="166"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+    </row>
+    <row r="8" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C8" s="230" t="s">
+        <v>217</v>
+      </c>
+      <c r="D8" s="231"/>
+      <c r="E8" s="231"/>
+      <c r="F8" s="231"/>
+      <c r="G8" s="231"/>
+      <c r="H8" s="231"/>
+      <c r="I8" s="231"/>
+      <c r="J8" s="232"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+    </row>
+    <row r="9" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C9" s="233"/>
+      <c r="D9" s="234"/>
+      <c r="E9" s="234"/>
+      <c r="F9" s="234"/>
+      <c r="G9" s="234"/>
+      <c r="H9" s="234"/>
+      <c r="I9" s="234"/>
+      <c r="J9" s="235"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="C48:J49"/>
+  <mergeCells count="1">
     <mergeCell ref="C8:J9"/>
-    <mergeCell ref="C16:J17"/>
-    <mergeCell ref="C24:J25"/>
-    <mergeCell ref="C32:J33"/>
-    <mergeCell ref="C40:J41"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="I21" r:id="rId1" xr:uid="{594C449D-3B6C-4B8F-B1F1-8C5EBB24B131}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>